--- a/public/templates/NPLatform_매물등록_템플릿.xlsx
+++ b/public/templates/NPLatform_매물등록_템플릿.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="199">
   <si>
     <t>[시트 1] 매물 기본 정보 — NPL 매물등록 템플릿 v3.0</t>
   </si>
@@ -418,6 +418,9 @@
     <t>채권원인서류 사본 (대출계약서·이행약정서)</t>
   </si>
   <si>
+    <t>선택</t>
+  </si>
+  <si>
     <t>예: 대출계약서.pdf</t>
   </si>
   <si>
@@ -427,6 +430,9 @@
     <t>등기부등본 (부동산 · 최근 1개월 내)</t>
   </si>
   <si>
+    <t>필수 자료 — 등기 권리관계 검증 근거</t>
+  </si>
+  <si>
     <t>건축물대장</t>
   </si>
   <si>
@@ -436,9 +442,6 @@
     <t>공시지가·시가표준액 확인</t>
   </si>
   <si>
-    <t>선택</t>
-  </si>
-  <si>
     <t>감정평가서 (공인감정평가법인)</t>
   </si>
   <si>
@@ -487,7 +490,7 @@
     <t>외관 전경 (주 정면)</t>
   </si>
   <si>
-    <t>최소 1장 · JPG/PNG · 2MB 이하 권장</t>
+    <t>필수 사진 — 최소 1장 · JPG/PNG · 2MB 이하 권장</t>
   </si>
   <si>
     <t>외관 측면 (골목·진입로)</t>
@@ -2093,14 +2096,14 @@
       <c r="B4" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>132</v>
+      <c r="C4" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2108,10 +2111,10 @@
         <v>132</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>132</v>
+        <v>136</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>9</v>
@@ -2125,7 +2128,7 @@
         <v>132</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>132</v>
@@ -2134,7 +2137,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>9</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2142,10 +2145,10 @@
         <v>132</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>132</v>
+        <v>139</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>9</v>
@@ -2159,10 +2162,10 @@
         <v>132</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>132</v>
+        <v>140</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>9</v>
@@ -2176,10 +2179,10 @@
         <v>132</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>132</v>
+        <v>141</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>9</v>
@@ -2190,30 +2193,30 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>9</v>
@@ -2224,13 +2227,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
@@ -2241,13 +2244,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>9</v>
@@ -2258,13 +2261,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>9</v>
@@ -2275,13 +2278,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>9</v>
@@ -2292,30 +2295,30 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>9</v>
@@ -2326,13 +2329,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>9</v>
@@ -2343,13 +2346,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>9</v>
@@ -2360,10 +2363,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>132</v>
@@ -2372,18 +2375,18 @@
         <v>9</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>9</v>
@@ -2394,13 +2397,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>9</v>
@@ -2411,13 +2414,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>9</v>
@@ -2428,13 +2431,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>9</v>
@@ -2445,13 +2448,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>9</v>
@@ -2462,13 +2465,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>9</v>
@@ -2516,7 +2519,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -2528,7 +2531,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="14"/>
     </row>
@@ -2537,7 +2540,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2545,7 +2548,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2553,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2564,7 +2567,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="14"/>
     </row>
@@ -2573,7 +2576,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2581,7 +2584,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2589,7 +2592,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2597,7 +2600,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2608,7 +2611,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" s="14"/>
     </row>
@@ -2617,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2625,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2633,7 +2636,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2641,7 +2644,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2652,7 +2655,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -2661,7 +2664,7 @@
         <v>9</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2669,7 +2672,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2677,7 +2680,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2685,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2693,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2701,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2712,7 +2715,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B28" s="14"/>
     </row>
@@ -2721,7 +2724,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2729,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2740,7 +2743,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" s="14"/>
     </row>
@@ -2749,7 +2752,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2757,7 +2760,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2768,7 +2771,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" s="14"/>
     </row>
@@ -2777,7 +2780,7 @@
         <v>9</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2785,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2793,7 +2796,7 @@
         <v>9</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2804,7 +2807,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" s="14"/>
     </row>
@@ -2813,7 +2816,7 @@
         <v>9</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/NPLatform_매물등록_템플릿.xlsx
+++ b/public/templates/NPLatform_매물등록_템플릿.xlsx
@@ -3,8 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="NPL 매물 등록" sheetId="1" r:id="rId1"/>
-    <sheet name="안내" sheetId="2" r:id="rId2"/>
+    <sheet name="01_표지" sheetId="1" r:id="rId1"/>
+    <sheet name="02_매각사" sheetId="2" r:id="rId2"/>
+    <sheet name="03_담보" sheetId="3" r:id="rId3"/>
+    <sheet name="04_채권" sheetId="4" r:id="rId4"/>
+    <sheet name="05_가치평가" sheetId="5" r:id="rId5"/>
+    <sheet name="06_매각조건" sheetId="6" r:id="rId6"/>
+    <sheet name="07_권리관계" sheetId="7" r:id="rId7"/>
+    <sheet name="08_특수조건" sheetId="8" r:id="rId8"/>
+    <sheet name="09_입력데이터" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -398,273 +405,270 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:A48"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="12.83203125" customWidth="1"/>
-    <col min="22" max="22" width="14.83203125" customWidth="1"/>
-    <col min="23" max="23" width="14.83203125" customWidth="1"/>
-    <col min="24" max="24" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>담보유형</v>
-      </c>
-      <c r="B1" t="str">
-        <v>담보주소</v>
-      </c>
-      <c r="C1" t="str">
-        <v>시도</v>
-      </c>
-      <c r="D1" t="str">
-        <v>시군구</v>
-      </c>
-      <c r="E1" t="str">
-        <v>최초 대출원금</v>
-      </c>
-      <c r="F1" t="str">
-        <v>대출원금 (현재)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>미수이자</v>
-      </c>
-      <c r="H1" t="str">
-        <v>연체이자</v>
-      </c>
-      <c r="I1" t="str">
-        <v>대출금리(%)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>연체금리(%)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>연체시작일</v>
-      </c>
-      <c r="L1" t="str">
-        <v>감정가</v>
-      </c>
-      <c r="M1" t="str">
-        <v>AI 시세 (선택)</v>
-      </c>
-      <c r="N1" t="str">
-        <v>매각 기준</v>
-      </c>
-      <c r="O1" t="str">
-        <v>매각 할인율(%)</v>
-      </c>
-      <c r="P1" t="str">
-        <v>희망매각가</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>수익권 금액(채권최고액)</v>
-      </c>
-      <c r="R1" t="str">
-        <v>1순위 권리자</v>
-      </c>
-      <c r="S1" t="str">
-        <v>1순위 채권최고액</v>
-      </c>
-      <c r="T1" t="str">
-        <v>전용면적(㎡)</v>
-      </c>
-      <c r="U1" t="str">
-        <v>채무자유형</v>
-      </c>
-      <c r="V1" t="str">
-        <v>입찰시작일</v>
-      </c>
-      <c r="W1" t="str">
-        <v>입찰마감일</v>
-      </c>
-      <c r="X1" t="str">
-        <v>특이사항</v>
+        <v>NPLATFORM · 매물 등록 템플릿</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>토지</v>
-      </c>
-      <c r="B2" t="str">
-        <v>서울특별시 종로구 홍지동 76-1번지 외 7필지(81-1, 81-4, 81-6, 81-7, 82, 83, 76-30)</v>
-      </c>
-      <c r="C2" t="str">
-        <v>서울특별시</v>
-      </c>
-      <c r="D2" t="str">
-        <v>종로구</v>
-      </c>
-      <c r="E2">
-        <v>1700000000</v>
-      </c>
-      <c r="F2">
-        <v>1648045960</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>81273499</v>
-      </c>
-      <c r="I2">
-        <v>18</v>
-      </c>
-      <c r="J2">
-        <v>20</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="L2">
-        <v>6673016000</v>
-      </c>
-      <c r="M2">
-        <v>7490203000</v>
-      </c>
-      <c r="N2" t="str">
-        <v>대출잔액</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>1729319459</v>
-      </c>
-      <c r="Q2">
-        <v>2380000000</v>
-      </c>
-      <c r="R2" t="str">
-        <v>농협은행</v>
-      </c>
-      <c r="S2">
-        <v>2364000000</v>
-      </c>
-      <c r="T2">
-        <v>5193</v>
-      </c>
-      <c r="U2" t="str">
-        <v>개인</v>
-      </c>
-      <c r="V2" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="W2" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="X2" t="str">
-        <v>8필지 일괄매각, 권리관계 깨끗 (1순위 농협 단독), 인근 1km 실거래 평균 273만원/㎡</v>
+        <v>Investment Memorandum · NPL Listing Submission Template</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>아파트</v>
-      </c>
-      <c r="B3" t="str">
-        <v>서울특별시 강남구 테헤란로 123 OO아파트 101동 1501호</v>
-      </c>
-      <c r="C3" t="str">
-        <v>서울특별시</v>
-      </c>
-      <c r="D3" t="str">
-        <v>강남구</v>
-      </c>
-      <c r="E3">
-        <v>1500000000</v>
-      </c>
-      <c r="F3">
-        <v>1500000000</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>35000000</v>
-      </c>
-      <c r="I3">
-        <v>6.5</v>
-      </c>
-      <c r="J3">
-        <v>9.5</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2025-12-15</v>
-      </c>
-      <c r="L3">
-        <v>1800000000</v>
-      </c>
-      <c r="M3">
-        <v>1750000000</v>
-      </c>
-      <c r="N3" t="str">
-        <v>대출원금</v>
-      </c>
-      <c r="O3">
-        <v>10</v>
-      </c>
-      <c r="P3">
-        <v>1350000000</v>
-      </c>
-      <c r="Q3">
-        <v>1800000000</v>
-      </c>
-      <c r="R3" t="str">
-        <v>KB국민은행</v>
-      </c>
-      <c r="S3">
-        <v>1800000000</v>
-      </c>
-      <c r="T3">
-        <v>84.97</v>
-      </c>
-      <c r="U3" t="str">
-        <v>법인</v>
-      </c>
-      <c r="V3" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="W3" t="str">
-        <v>2026-04-30</v>
-      </c>
-      <c r="X3" t="str">
-        <v>선순위 근저당 1건, 임차인 2명 거주 (보증금 2.5억)</v>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Phase G7+ · 2026-04-28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>(주) 트랜스파머 · NPLatform Engineering</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>── 사용 안내 ──────────────────────────────────────────────────</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1. 본 템플릿은 9개 Sheet 로 구성되어 있습니다.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">   · Sheet 02 ~ Sheet 08 까지 매각사가 직접 작성</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">   · Sheet 09 (입력 데이터) 는 시스템 업로드용 1-row payload (자동 생성 가능)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2. 셀 입력 규칙</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">   · 금액: 원 단위 정수 (1648045960 — 콤마/단위 표기 X)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve">   · 금리: 소수점 2자리 (18.00 — % 기호 X)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve">   · 날짜: YYYY-MM-DD (2026-04-28)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">   · 드롭다운 옵션은 Sheet 별 안내 참고</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>3. 핵심 정책 (NPLatform 공식)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve">   · 채권잔액 = 대출원금 (현재) + 미수이자 + 연체이자</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">   · 매각 기준: 대출원금 OR 대출잔액 중 1개 선택</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">     - 대출원금 기준 → 매각가 = 대출원금 × (1 − 할인율)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">     - 대출잔액 기준 → 매각가 = 채권잔액 × (1 − 할인율)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">   · 수익권 금액 (공부상 채권최고액) = 최초 대출원금 × 110~140%</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">     ※ 일부 상환된 경우 ≠ (현재) 대출원금 × 1.4 — 반드시 최초 원금 base</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">   · LTV = (선순위 채권최고액 + 대출원금) / 감정가</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>4. 업로드 흐름</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">   · 본 파일을 NPLatform 매물 등록 페이지(/exchange/sell)에서 업로드</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">   · OCR 자동 파싱 → 9개 Sheet 데이터 → 폼 자동 채움</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">   · 사용자 검토 → 등록 완료</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>── 시트 구성 ──────────────────────────────────────────────────</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Sheet 01 · 표지 (현재 시트)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Sheet 02 · 매각사 정보 (institution) — 채권자/판매자</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Sheet 03 · 담보 정보 (collateral) — 주소/면적/유형</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Sheet 04 · 채권 정보 (claim) — 최초/현재 원금, 이자, 금리</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Sheet 05 · 가치 평가 (appraisal) — 감정가/AI 시세</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Sheet 06 · 매각 조건 (sale) — 기준 옵션 + 할인율 + 매각가</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Sheet 07 · 권리관계 (rights) — 선/후순위 + 임차 현황</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Sheet 08 · 특수조건 V2 (special_conditions) — 18항목 체크리스트</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Sheet 09 · 입력 데이터 (payload) — 1-row 통합 데이터 (시스템 업로드용)</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>── 문의 ─────────────────────────────────────────────────────</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>NPLatform 매각사 지원: biz@transfarmer.co.kr</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:C11"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>NPLatform 매물 등록 템플릿 — Phase G7+ (2026-04-28)</v>
+        <v>Sheet 02 · 매각사 정보 (Institution)</v>
       </c>
     </row>
     <row r="2">
@@ -674,7 +678,302 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>[ 채권 구조 ]</v>
+        <v>항목</v>
+      </c>
+      <c r="B3" t="str">
+        <v>값</v>
+      </c>
+      <c r="C3" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>매각사명</v>
+      </c>
+      <c r="B4" t="str">
+        <v>주식회사 에이에프투자대부</v>
+      </c>
+      <c r="C4" t="str">
+        <v>실명 입력 (시스템에서 마스킹 처리)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>매각사 유형</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MONEY_LENDER</v>
+      </c>
+      <c r="C5" t="str">
+        <v>BANK / SAVINGS_BANK / MUTUAL_CREDIT / AMC / MONEY_LENDER / FUND / SECURITIES / INSURANCE / CAPITAL / CREDIT_CARD / INDIVIDUAL / CORPORATION</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>매각 카테고리</v>
+      </c>
+      <c r="B6" t="str">
+        <v>NPL</v>
+      </c>
+      <c r="C6" t="str">
+        <v>NPL / REO / UPL</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>전속 매각 여부</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="C7" t="str">
+        <v>TRUE/FALSE — NPLatform 단독 매각 시 TRUE</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>담당자명</v>
+      </c>
+      <c r="B8" t="str">
+        <v>○○○</v>
+      </c>
+      <c r="C8" t="str">
+        <v>실명 (마스킹 처리)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>담당자 연락처</v>
+      </c>
+      <c r="B9" t="str">
+        <v>02-XXXX-XXXX</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>담당자 이메일</v>
+      </c>
+      <c r="B10" t="str">
+        <v>contact@example.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>기준일</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>채권잔액·연체이자 계산 기준일 YYYY-MM-DD</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="70.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet 03 · 담보 정보 (Collateral)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B3" t="str">
+        <v>값</v>
+      </c>
+      <c r="C3" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>담보유형</v>
+      </c>
+      <c r="B4" t="str">
+        <v>토지</v>
+      </c>
+      <c r="C4" t="str">
+        <v>아파트 / 오피스텔 / 다세대(빌라) / 단독주택 / 상가 / 사무실 / 공장 / 창고 / 토지 / 임야 / 호텔 / 기타</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>시도</v>
+      </c>
+      <c r="B5" t="str">
+        <v>서울특별시</v>
+      </c>
+      <c r="C5" t="str">
+        <v>드롭다운</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>시군구</v>
+      </c>
+      <c r="B6" t="str">
+        <v>종로구</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>읍면동/상세주소</v>
+      </c>
+      <c r="B7" t="str">
+        <v>홍지동 76-1번지 외 7필지(81-1, 81-4, 81-6, 81-7, 82, 83, 76-30)</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>전체 주소 (한 줄)</v>
+      </c>
+      <c r="B8" t="str">
+        <v>서울특별시 종로구 홍지동 76-1번지 외 7필지</v>
+      </c>
+      <c r="C8" t="str">
+        <v>시스템 자동 합성 가능</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>전용면적 (㎡)</v>
+      </c>
+      <c r="B9">
+        <v>5193</v>
+      </c>
+      <c r="C9" t="str">
+        <v>소수점 2자리</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>공급면적 (㎡)</v>
+      </c>
+      <c r="B10">
+        <v>5193</v>
+      </c>
+      <c r="C10" t="str">
+        <v>토지일 경우 동일</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>용도지역</v>
+      </c>
+      <c r="B11" t="str">
+        <v>제1종일반주거지역</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>추가 주소 (포트폴리오)</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>복합 담보일 경우 줄바꿈으로 추가 주소 나열</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>채무자 유형</v>
+      </c>
+      <c r="B13" t="str">
+        <v>개인</v>
+      </c>
+      <c r="C13" t="str">
+        <v>개인 / 법인</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>채무자명</v>
+      </c>
+      <c r="B14" t="str">
+        <v>박**</v>
+      </c>
+      <c r="C14" t="str">
+        <v>마스킹 처리된 이름 (시스템에서 추가 마스킹)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>채무자·소유자 동일</v>
+      </c>
+      <c r="B15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="C15" t="str">
+        <v>TRUE/FALSE</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D19"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="50.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet 04 · 채권 정보 (Claim)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>【 핵심 정책 】</v>
       </c>
     </row>
     <row r="4">
@@ -684,12 +983,12 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">  · 매입 시점 채권잔액 = 매수자가 인수하는 총 채권액</v>
+        <v xml:space="preserve">  · 최초 대출원금 ≠ 대출원금 (현재) — 일부 상환된 경우</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">  · 최초 대출원금 ≠ 대출원금 (현재) — 일부 상환 시 &lt; 최초</v>
+        <v xml:space="preserve">  · 수익권 금액(채권최고액) = 최초 대출원금 × 110~140%</v>
       </c>
     </row>
     <row r="7">
@@ -699,147 +998,1808 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>[ 매각 기준 ]</v>
+        <v>항목</v>
+      </c>
+      <c r="B8" t="str">
+        <v>값</v>
+      </c>
+      <c r="C8" t="str">
+        <v>단위 / 옵션</v>
+      </c>
+      <c r="D8" t="str">
+        <v>비고</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">  · 대출원금 기준  : 매각가 = 대출원금 × (1 − 할인율)</v>
+        <v>최초 대출원금</v>
+      </c>
+      <c r="B9">
+        <v>1700000000</v>
+      </c>
+      <c r="C9" t="str">
+        <v>원</v>
+      </c>
+      <c r="D9" t="str">
+        <v>대출 약정 시점 원금. 수익권 base</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  · 대출잔액 기준  : 매각가 = 채권잔액 × (1 − 할인율)</v>
+        <v>대출원금 (현재)</v>
+      </c>
+      <c r="B10">
+        <v>1648045960</v>
+      </c>
+      <c r="C10" t="str">
+        <v>원</v>
+      </c>
+      <c r="D10" t="str">
+        <v>일부 상환된 경우 &lt; 최초 대출원금</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">  · 잔액 100% 매각 = "대출잔액" + 할인율 0%</v>
+        <v>미수이자 (정상이자 누적)</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11" t="str">
+        <v>원</v>
+      </c>
+      <c r="D11" t="str">
+        <v>없으면 0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>연체이자 (매입 시점 누적)</v>
+      </c>
+      <c r="B12">
+        <v>81273499</v>
+      </c>
+      <c r="C12" t="str">
+        <v>원</v>
+      </c>
+      <c r="D12" t="str">
+        <v>기준일 기준 누적 연체이자</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>[ 수익권 금액 (공부상 채권최고액) ]</v>
+        <v>채권잔액 (자동 계산)</v>
+      </c>
+      <c r="B13">
+        <v>1729319459</v>
+      </c>
+      <c r="C13" t="str">
+        <v>원</v>
+      </c>
+      <c r="D13" t="str">
+        <v>= 대출원금 + 미수이자 + 연체이자</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">  · 산정식: 최초 대출원금 × 110% ~ 140% (1차 근저당 표준)</v>
+        <v>대출 금리 (정상)</v>
+      </c>
+      <c r="B14">
+        <v>18</v>
+      </c>
+      <c r="C14" t="str">
+        <v>% (소수점 2자리)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>약정 금리</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">  · 일부 상환된 경우 ≠ (현재) 대출원금 × 1.4</v>
+        <v>연체 금리</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>% (소수점 2자리)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>연체 시점부터 적용</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">  · 한국법: 채권최고액 = 원금 × 1.2 (default), 약정에 따라 1.1~1.4</v>
+        <v>연체 시작일</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="C16" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>기한이익상실일</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="C17" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D17" t="str">
+        <v>없으면 연체시작 + 60일 자동</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>[ 권리관계 ]</v>
+        <v>수익권금액 (공부상 채권최고액)</v>
+      </c>
+      <c r="B18">
+        <v>2380000000</v>
+      </c>
+      <c r="C18" t="str">
+        <v>원</v>
+      </c>
+      <c r="D18" t="str">
+        <v>= 최초 대출원금 × 110~140% (1차 근저당 표준)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">  · 1순위 권리자 / 1순위 채권최고액 = 선순위 근저당</v>
+        <v>수익권 multiplier</v>
+      </c>
+      <c r="B19">
+        <v>1.4</v>
+      </c>
+      <c r="C19" t="str">
+        <v>소수 (1.10 ~ 1.40)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>수익권금액 / 최초 대출원금</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D10"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="50.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet 05 · 가치 평가 (Appraisal &amp; Market Value)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B3" t="str">
+        <v>값</v>
+      </c>
+      <c r="C3" t="str">
+        <v>단위</v>
+      </c>
+      <c r="D3" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>감정가 (공부)</v>
+      </c>
+      <c r="B4">
+        <v>6673016000</v>
+      </c>
+      <c r="C4" t="str">
+        <v>원</v>
+      </c>
+      <c r="D4" t="str">
+        <v>감정평가서 기준</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>감정평가일</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AI 시세 (현재)</v>
+      </c>
+      <c r="B6">
+        <v>7490203000</v>
+      </c>
+      <c r="C6" t="str">
+        <v>원</v>
+      </c>
+      <c r="D6" t="str">
+        <v>NPLatform AI 또는 외부 시세</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AI 시세 메모</v>
+      </c>
+      <c r="B7" t="str">
+        <v>인근 1km 실거래 평균 273만원/㎡</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>근거 출처</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LTV</v>
+      </c>
+      <c r="B8">
+        <v>60.12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>%</v>
+      </c>
+      <c r="D8" t="str">
+        <v>= (선순위 + 대출원금) / 감정가 × 100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>예상 낙찰가율</v>
+      </c>
+      <c r="B9">
+        <v>71.4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>% (3개월 평균)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>지역·물건 통계 기반</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>경매개시결정일</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C10" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D10" t="str">
+        <v>없으면 빈칸</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D27"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="36.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet 06 · 매각 조건 (Sale Terms)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>【 매각 기준 옵션 】</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">  옵션 A — 대출원금 기준  : 매각가 = 대출원금 (현재) × (1 − 할인율 A)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">  옵션 B — 대출잔액 기준  : 매각가 = 채권잔액 × (1 − 할인율 B)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">  ※ 매각사가 둘 중 하나만 선택. 양쪽 모두 작성한 경우 "매각 기준" 컬럼이 우선.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B8" t="str">
+        <v>값</v>
+      </c>
+      <c r="C8" t="str">
+        <v>단위 / 옵션</v>
+      </c>
+      <c r="D8" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>매각 기준</v>
+      </c>
+      <c r="B9" t="str">
+        <v>대출잔액</v>
+      </c>
+      <c r="C9" t="str">
+        <v>PRINCIPAL(대출원금) / CLAIM_BALANCE(대출잔액)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>둘 중 1개 선택</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>── 옵션 A · 대출원금 기준 ─────────────────────────────────────</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>할인율 (대출원금 대비)</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>% (소수점 2자리)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0% = 대출원금 전액 매각가 / 5% = 5% 할인</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>매각희망가 (대출원금 기준)</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>원</v>
+      </c>
+      <c r="D13" t="str">
+        <v>= 대출원금 × (1 − 할인율 A) — 자동 계산 가능</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>── 옵션 B · 대출잔액 기준 ─────────────────────────────────────</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>할인율 (대출잔액 대비)</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" t="str">
+        <v>% (소수점 2자리)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>0% = 채권잔액 전액 매각가</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>매각희망가 (대출잔액 기준)</v>
+      </c>
+      <c r="B17">
+        <v>1729319459</v>
+      </c>
+      <c r="C17" t="str">
+        <v>원</v>
+      </c>
+      <c r="D17" t="str">
+        <v>= 채권잔액 × (1 − 할인율 B)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>── 공통 ─────────────────────────────────────────────────────────</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">  · NPL 매수자가 변제 의무 (낙찰가 → 1순위 변제 후 잔여가 NPL 회수액)</v>
+        <v>최저매각가</v>
+      </c>
+      <c r="B20">
+        <v>1729319459</v>
+      </c>
+      <c r="C20" t="str">
+        <v>원</v>
+      </c>
+      <c r="D20" t="str">
+        <v>경매 시 최저매각가</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">  · LTV = (선순위 채권최고액 + 대출원금) / 감정가</v>
+        <v>계약금</v>
+      </c>
+      <c r="B21">
+        <v>172931946</v>
+      </c>
+      <c r="C21" t="str">
+        <v>원</v>
+      </c>
+      <c r="D21" t="str">
+        <v>매각가 × 10% (자동 계산)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>계약일</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C22" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>[ AI 권고 매입가 — 3-단계 시나리오 ]</v>
+        <v>잔금일</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C23" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">  · 보수적: base × 90%   (낙찰가율 평균 −2σ — 하락 방어)</v>
+        <v>매각 방식</v>
+      </c>
+      <c r="B24" t="str">
+        <v>일괄매각</v>
+      </c>
+      <c r="C24" t="str">
+        <v>일괄매각 / 분할매각 / 경매 / 협의매각</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">  · 표준  : base × 95%   (낙찰가율 평균)</v>
+        <v>공개 가시성</v>
+      </c>
+      <c r="B25" t="str">
+        <v>PUBLIC</v>
+      </c>
+      <c r="C25" t="str">
+        <v>PUBLIC / MEMBERS / VIP / TARGETED</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  · 공격적: base × 100%  (낙찰가율 평균 +0.7σ — 상승 포지셔닝)</v>
+        <v>매도자 수수료율</v>
+      </c>
+      <c r="B26">
+        <v>0.005</v>
+      </c>
+      <c r="C26" t="str">
+        <v>소수 (0.003 ~ 0.009)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>0.5% (default), 0.3~0.9% 범위</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  · AI 권고 표시 = ROI ≥ 30% (성공확률 무관)</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>[ 입력 가이드 ]</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v xml:space="preserve">  · 매각 기준: "대출원금" 또는 "대출잔액" 중 1개만 선택</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v xml:space="preserve">  · 채무자유형: "개인" 또는 "법인"</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v xml:space="preserve">  · 날짜: YYYY-MM-DD 형식 (예: 2026-04-28)</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v xml:space="preserve">  · 금액: 원 단위 정수 (콤마 X, 단위 X — 1648045960 처럼)</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">  · 금리: 소수점 2자리 (18.00 처럼, % 기호 X)</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v xml:space="preserve">  · 미수이자/연체이자: 0 입력 가능 (값 없으면 0)</v>
+        <v>공개 마감일</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C27" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D19"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet 07 · 권리관계 (Rights)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>【 LTV 산정식 】</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">  LTV = (선순위 채권최고액 + 대출원금) / 감정가 × 100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B6" t="str">
+        <v>값</v>
+      </c>
+      <c r="C6" t="str">
+        <v>단위</v>
+      </c>
+      <c r="D6" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1순위 권리자</v>
+      </c>
+      <c r="B7" t="str">
+        <v>농협은행</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>실명 입력 (시스템 처리)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1순위 권리 종류</v>
+      </c>
+      <c r="B8" t="str">
+        <v>근저당권</v>
+      </c>
+      <c r="C8" t="str">
+        <v>근저당권 / 전세권 / 가압류 / 가처분 / 임차권 / 압류</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1순위 채권최고액</v>
+      </c>
+      <c r="B9">
+        <v>2364000000</v>
+      </c>
+      <c r="C9" t="str">
+        <v>원</v>
+      </c>
+      <c r="D9" t="str">
+        <v>설정금액</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1순위 설정일</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2024-09-03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>YYYY-MM-DD</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>후순위 권리자 수</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12" t="str">
+        <v>건</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0이면 후순위 없음</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>후순위 채권최고액 합계</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13" t="str">
+        <v>원</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>── 임차 현황 ────────────────────────────────────────────</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>임차인 수</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" t="str">
+        <v>명</v>
+      </c>
+      <c r="D16" t="str">
+        <v>0 = 임차인 없음</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>보증금 합계</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" t="str">
+        <v>원</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>월세 합계</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" t="str">
+        <v>원</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>공실 여부</v>
+      </c>
+      <c r="B19" t="str">
+        <v>해당사항 없음</v>
+      </c>
+      <c r="C19" t="str">
+        <v>공실 / 임차 / 해당사항 없음</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F24"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet 08 · 특수조건 V2 18항목 (Special Conditions)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>【 사용법 】 해당 셀에 O / TRUE / 1 입력 시 체크. 빈칸 / X / FALSE / 0 = 미체크.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>【 권리관계 점수 】 max(20, 100 − Σ감점)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>카테고리</v>
+      </c>
+      <c r="B6" t="str">
+        <v>항목</v>
+      </c>
+      <c r="C6" t="str">
+        <v>키 (시스템)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>감점</v>
+      </c>
+      <c r="E6" t="str">
+        <v>체크</v>
+      </c>
+      <c r="F6" t="str">
+        <v>설명</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>🔴 소유권 리스크</v>
+      </c>
+      <c r="B7" t="str">
+        <v>전세권만 매각</v>
+      </c>
+      <c r="C7" t="str">
+        <v>leasehold_only_sale</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>전세권 단독 경매 · 소유권 이전 불가</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>🔴 소유권 리스크</v>
+      </c>
+      <c r="B8" t="str">
+        <v>선순위 등기권리 존재</v>
+      </c>
+      <c r="C8" t="str">
+        <v>senior_registry_rights</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8" t="str">
+        <v>O</v>
+      </c>
+      <c r="F8" t="str">
+        <v>선순위 근저당·지상권·임차권 등</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>🔴 소유권 리스크</v>
+      </c>
+      <c r="B9" t="str">
+        <v>대항력 있는 임차인</v>
+      </c>
+      <c r="C9" t="str">
+        <v>opposable_tenant</v>
+      </c>
+      <c r="D9">
+        <v>45</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>주택임대차보호법 · 보증금 인수</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>🔴 소유권 리스크</v>
+      </c>
+      <c r="B10" t="str">
+        <v>유치권 / 법정지상권</v>
+      </c>
+      <c r="C10" t="str">
+        <v>lien_or_statutory_easement</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>제3자 점유 · 명도 제한</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>🔴 소유권 리스크</v>
+      </c>
+      <c r="B11" t="str">
+        <v>지분입찰</v>
+      </c>
+      <c r="C11" t="str">
+        <v>share_auction</v>
+      </c>
+      <c r="D11">
+        <v>40</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>공유지분만 매각</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B12" t="str">
+        <v>당해세</v>
+      </c>
+      <c r="C12" t="str">
+        <v>inherent_tax</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>해당 부동산 부과 조세 · 최우선 배당</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B13" t="str">
+        <v>토지 별도등기</v>
+      </c>
+      <c r="C13" t="str">
+        <v>land_separate_registry</v>
+      </c>
+      <c r="D13">
+        <v>35</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>건물·토지 등기 분리</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B14" t="str">
+        <v>임금채권</v>
+      </c>
+      <c r="C14" t="str">
+        <v>wage_claim</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>최종 3개월분 + 퇴직금 3년분</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B15" t="str">
+        <v>임차권 등기</v>
+      </c>
+      <c r="C15" t="str">
+        <v>lease_registration</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>대항력 유지 · 보증금 인수</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B16" t="str">
+        <v>대지권 미등기</v>
+      </c>
+      <c r="C16" t="str">
+        <v>site_right_unregistered</v>
+      </c>
+      <c r="D16">
+        <v>30</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>건물만 매각 · 대지사용권 별도</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B17" t="str">
+        <v>조세 / 4대보험</v>
+      </c>
+      <c r="C17" t="str">
+        <v>tax_and_social_insurance</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>국세·지방세·국민연금 체납</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>🟠 비용 리스크</v>
+      </c>
+      <c r="B18" t="str">
+        <v>재해보상</v>
+      </c>
+      <c r="C18" t="str">
+        <v>disaster_compensation</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>산재 보상금 체납</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>🟡 유동성 리스크</v>
+      </c>
+      <c r="B19" t="str">
+        <v>무허가건축물</v>
+      </c>
+      <c r="C19" t="str">
+        <v>illegal_building</v>
+      </c>
+      <c r="D19">
+        <v>45</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>건축허가 無 · 철거 대상</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>🟡 유동성 리스크</v>
+      </c>
+      <c r="B20" t="str">
+        <v>맹지</v>
+      </c>
+      <c r="C20" t="str">
+        <v>landlocked</v>
+      </c>
+      <c r="D20">
+        <v>35</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>도로 접근 無 · 건축 제약</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>🟡 유동성 리스크</v>
+      </c>
+      <c r="B21" t="str">
+        <v>사용승인 미필</v>
+      </c>
+      <c r="C21" t="str">
+        <v>no_use_approval</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>준공검사 미완료</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>🟡 유동성 리스크</v>
+      </c>
+      <c r="B22" t="str">
+        <v>분묘기지권</v>
+      </c>
+      <c r="C22" t="str">
+        <v>grave_base_right</v>
+      </c>
+      <c r="D22">
+        <v>30</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>타인 묘지 존재 (토지 한정)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>🟡 유동성 리스크</v>
+      </c>
+      <c r="B23" t="str">
+        <v>위반건축물</v>
+      </c>
+      <c r="C23" t="str">
+        <v>code_violation</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>건축물대장 등재 · 양성화비</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>🟡 유동성 리스크</v>
+      </c>
+      <c r="B24" t="str">
+        <v>농취증 필요</v>
+      </c>
+      <c r="C24" t="str">
+        <v>farmland_qualification</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>농지법 제8조 · 취득자격 제한</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F24"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BQ2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col min="13" max="13" width="22.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="22.83203125" customWidth="1"/>
+    <col min="16" max="16" width="22.83203125" customWidth="1"/>
+    <col min="17" max="17" width="22.83203125" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" customWidth="1"/>
+    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" customWidth="1"/>
+    <col min="21" max="21" width="22.83203125" customWidth="1"/>
+    <col min="22" max="22" width="22.83203125" customWidth="1"/>
+    <col min="23" max="23" width="22.83203125" customWidth="1"/>
+    <col min="24" max="24" width="22.83203125" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" customWidth="1"/>
+    <col min="26" max="26" width="22.83203125" customWidth="1"/>
+    <col min="27" max="27" width="22.83203125" customWidth="1"/>
+    <col min="28" max="28" width="22.83203125" customWidth="1"/>
+    <col min="29" max="29" width="22.83203125" customWidth="1"/>
+    <col min="30" max="30" width="22.83203125" customWidth="1"/>
+    <col min="31" max="31" width="22.83203125" customWidth="1"/>
+    <col min="32" max="32" width="22.83203125" customWidth="1"/>
+    <col min="33" max="33" width="22.83203125" customWidth="1"/>
+    <col min="34" max="34" width="22.83203125" customWidth="1"/>
+    <col min="35" max="35" width="22.83203125" customWidth="1"/>
+    <col min="36" max="36" width="22.83203125" customWidth="1"/>
+    <col min="37" max="37" width="22.83203125" customWidth="1"/>
+    <col min="38" max="38" width="22.83203125" customWidth="1"/>
+    <col min="39" max="39" width="22.83203125" customWidth="1"/>
+    <col min="40" max="40" width="22.83203125" customWidth="1"/>
+    <col min="41" max="41" width="22.83203125" customWidth="1"/>
+    <col min="42" max="42" width="22.83203125" customWidth="1"/>
+    <col min="43" max="43" width="22.83203125" customWidth="1"/>
+    <col min="44" max="44" width="22.83203125" customWidth="1"/>
+    <col min="45" max="45" width="22.83203125" customWidth="1"/>
+    <col min="46" max="46" width="22.83203125" customWidth="1"/>
+    <col min="47" max="47" width="22.83203125" customWidth="1"/>
+    <col min="48" max="48" width="22.83203125" customWidth="1"/>
+    <col min="49" max="49" width="22.83203125" customWidth="1"/>
+    <col min="50" max="50" width="22.83203125" customWidth="1"/>
+    <col min="51" max="51" width="22.83203125" customWidth="1"/>
+    <col min="52" max="52" width="22.83203125" customWidth="1"/>
+    <col min="53" max="53" width="22.83203125" customWidth="1"/>
+    <col min="54" max="54" width="22.83203125" customWidth="1"/>
+    <col min="55" max="55" width="22.83203125" customWidth="1"/>
+    <col min="56" max="56" width="22.83203125" customWidth="1"/>
+    <col min="57" max="57" width="22.83203125" customWidth="1"/>
+    <col min="58" max="58" width="22.83203125" customWidth="1"/>
+    <col min="59" max="59" width="22.83203125" customWidth="1"/>
+    <col min="60" max="60" width="22.83203125" customWidth="1"/>
+    <col min="61" max="61" width="22.83203125" customWidth="1"/>
+    <col min="62" max="62" width="22.83203125" customWidth="1"/>
+    <col min="63" max="63" width="22.83203125" customWidth="1"/>
+    <col min="64" max="64" width="22.83203125" customWidth="1"/>
+    <col min="65" max="65" width="22.83203125" customWidth="1"/>
+    <col min="66" max="66" width="22.83203125" customWidth="1"/>
+    <col min="67" max="67" width="22.83203125" customWidth="1"/>
+    <col min="68" max="68" width="22.83203125" customWidth="1"/>
+    <col min="69" max="69" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>institution_name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>institution_type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>listing_category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>is_exclusive</v>
+      </c>
+      <c r="E1" t="str">
+        <v>reference_date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>collateral_type</v>
+      </c>
+      <c r="G1" t="str">
+        <v>sido</v>
+      </c>
+      <c r="H1" t="str">
+        <v>sigungu</v>
+      </c>
+      <c r="I1" t="str">
+        <v>address</v>
+      </c>
+      <c r="J1" t="str">
+        <v>land_area</v>
+      </c>
+      <c r="K1" t="str">
+        <v>building_area</v>
+      </c>
+      <c r="L1" t="str">
+        <v>zoning</v>
+      </c>
+      <c r="M1" t="str">
+        <v>debtor_type</v>
+      </c>
+      <c r="N1" t="str">
+        <v>debtor_owner_same</v>
+      </c>
+      <c r="O1" t="str">
+        <v>initial_principal</v>
+      </c>
+      <c r="P1" t="str">
+        <v>loan_principal</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>unpaid_interest</v>
+      </c>
+      <c r="R1" t="str">
+        <v>overdue_interest</v>
+      </c>
+      <c r="S1" t="str">
+        <v>normal_rate</v>
+      </c>
+      <c r="T1" t="str">
+        <v>overdue_rate</v>
+      </c>
+      <c r="U1" t="str">
+        <v>delinquency_start_date</v>
+      </c>
+      <c r="V1" t="str">
+        <v>acceleration_date</v>
+      </c>
+      <c r="W1" t="str">
+        <v>beneficial_amount</v>
+      </c>
+      <c r="X1" t="str">
+        <v>max_bond_multiplier</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>appraisal_value</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>appraisal_date</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>ai_market_value</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>ltv_ratio</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>expected_bid_ratio</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>discount_basis</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>discount_rate_principal</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>discount_rate_balance</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>asking_price</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>minimum_bid</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>contract_amount</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>contract_date</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>closing_date</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>sale_method</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>visibility</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>seller_fee_rate</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>deadline</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>rights_priority_1</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>rights_kind_1</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>max_claim_amount</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>rights_setup_date_1</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>subordinate_count</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>subordinate_total_amount</v>
+      </c>
+      <c r="AV1" t="str">
+        <v>tenant_count</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>deposit</v>
+      </c>
+      <c r="AX1" t="str">
+        <v>monthly_rent</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>vacancy_status</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>sc_leasehold_only_sale</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>sc_senior_registry_rights</v>
+      </c>
+      <c r="BB1" t="str">
+        <v>sc_opposable_tenant</v>
+      </c>
+      <c r="BC1" t="str">
+        <v>sc_lien_or_statutory_easement</v>
+      </c>
+      <c r="BD1" t="str">
+        <v>sc_share_auction</v>
+      </c>
+      <c r="BE1" t="str">
+        <v>sc_inherent_tax</v>
+      </c>
+      <c r="BF1" t="str">
+        <v>sc_land_separate_registry</v>
+      </c>
+      <c r="BG1" t="str">
+        <v>sc_wage_claim</v>
+      </c>
+      <c r="BH1" t="str">
+        <v>sc_lease_registration</v>
+      </c>
+      <c r="BI1" t="str">
+        <v>sc_site_right_unregistered</v>
+      </c>
+      <c r="BJ1" t="str">
+        <v>sc_tax_and_social_insurance</v>
+      </c>
+      <c r="BK1" t="str">
+        <v>sc_disaster_compensation</v>
+      </c>
+      <c r="BL1" t="str">
+        <v>sc_illegal_building</v>
+      </c>
+      <c r="BM1" t="str">
+        <v>sc_landlocked</v>
+      </c>
+      <c r="BN1" t="str">
+        <v>sc_no_use_approval</v>
+      </c>
+      <c r="BO1" t="str">
+        <v>sc_grave_base_right</v>
+      </c>
+      <c r="BP1" t="str">
+        <v>sc_code_violation</v>
+      </c>
+      <c r="BQ1" t="str">
+        <v>sc_farmland_qualification</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>주식회사 에이에프투자대부</v>
+      </c>
+      <c r="B2" t="str">
+        <v>MONEY_LENDER</v>
+      </c>
+      <c r="C2" t="str">
+        <v>NPL</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="F2" t="str">
+        <v>토지</v>
+      </c>
+      <c r="G2" t="str">
+        <v>서울특별시</v>
+      </c>
+      <c r="H2" t="str">
+        <v>종로구</v>
+      </c>
+      <c r="I2" t="str">
+        <v>서울특별시 종로구 홍지동 76-1번지 외 7필지(81-1, 81-4, 81-6, 81-7, 82, 83, 76-30)</v>
+      </c>
+      <c r="J2">
+        <v>5193</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="str">
+        <v>제1종일반주거지역</v>
+      </c>
+      <c r="M2" t="str">
+        <v>개인</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1700000000</v>
+      </c>
+      <c r="P2">
+        <v>1648045960</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>81273499</v>
+      </c>
+      <c r="S2">
+        <v>18</v>
+      </c>
+      <c r="T2">
+        <v>20</v>
+      </c>
+      <c r="U2" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="V2" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="W2">
+        <v>2380000000</v>
+      </c>
+      <c r="X2">
+        <v>1.4</v>
+      </c>
+      <c r="Y2">
+        <v>6673016000</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="AA2">
+        <v>7490203000</v>
+      </c>
+      <c r="AB2">
+        <v>60.12</v>
+      </c>
+      <c r="AC2">
+        <v>71.4</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>CLAIM_BALANCE</v>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>1729319459</v>
+      </c>
+      <c r="AH2">
+        <v>1729319459</v>
+      </c>
+      <c r="AI2">
+        <v>172931946</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>일괄매각</v>
+      </c>
+      <c r="AM2" t="str">
+        <v>PUBLIC</v>
+      </c>
+      <c r="AN2">
+        <v>0.005</v>
+      </c>
+      <c r="AO2" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="AP2" t="str">
+        <v>농협은행</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v>근저당권</v>
+      </c>
+      <c r="AR2">
+        <v>2364000000</v>
+      </c>
+      <c r="AS2" t="str">
+        <v>2024-09-03</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="str">
+        <v>해당사항 없음</v>
+      </c>
+      <c r="AZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:BQ2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/NPLatform_매물등록_템플릿.xlsx
+++ b/public/templates/NPLatform_매물등록_템플릿.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="245">
-  <si>
-    <t>[시트 1] 매물 기본 정보 — NPL 매물등록 템플릿 v3.2 (드롭다운+O/X+수식)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="252">
+  <si>
+    <t>[시트 1] 매물 기본 정보 — NPL 매물등록 템플릿 v3.3 (드롭다운+O/X+수식+수익권 커스텀)</t>
   </si>
   <si>
     <t>항목</t>
@@ -154,10 +154,22 @@
     <t>= 대출원금 + 미수이자 + 연체이자</t>
   </si>
   <si>
-    <t>수익권금액 (원) · 자동 · 최초원금 ×140%</t>
-  </si>
-  <si>
-    <t>1차 근저당 수익권금액 = 최초 대출원금 × 110~140% (표준 140%)</t>
+    <t>수익권 비율 (%)</t>
+  </si>
+  <si>
+    <t>1차 근저당 표준 110~140%. 본인이 설정 가능 (기본 140)</t>
+  </si>
+  <si>
+    <t>수익권금액 (자동 계산값 · 참고)</t>
+  </si>
+  <si>
+    <t>= 최초 대출원금 × 수익권 비율% (참고용 자동값)</t>
+  </si>
+  <si>
+    <t>수익권금액 (적용값 · 직접 입력)</t>
+  </si>
+  <si>
+    <t>비워두면 위 자동값 적용. 매도자 협상가 또는 등기부 채권최고액 직접 입력 가능</t>
   </si>
   <si>
     <t>연체 시작일</t>
@@ -595,7 +607,7 @@
     <t>건물대장·등기부 사진 또는 스캔</t>
   </si>
   <si>
-    <t>[시트 4] 입력 가이드 · OCR 규격 (v3.2 · 드롭다운 + O/X + 자동계산 수식)</t>
+    <t>[시트 4] 입력 가이드 · OCR 규격 (v3.3 · 드롭다운 + O/X + 자동계산 + 수익권 커스텀)</t>
   </si>
   <si>
     <t>1. 입력 형식 구분</t>
@@ -619,7 +631,13 @@
     <t>· 채권잔액 = 대출원금 + 미수이자 + 연체이자</t>
   </si>
   <si>
-    <t>· 수익권금액 = 최초 대출원금 × 140% (1차 근저당 표준)</t>
+    <t>· 수익권 비율 (%) = 본인 설정 (110~140 표준 · 기본 140)</t>
+  </si>
+  <si>
+    <t>· 수익권금액 (자동값) = 최초 대출원금 × 수익권 비율%</t>
+  </si>
+  <si>
+    <t>· 수익권금액 (적용값) = 직접 입력 가능 (비우면 자동값 적용 · 매도자 협상가/등기부 채권최고액 우선 시 사용)</t>
   </si>
   <si>
     <t>· 매각가 옵션 A = 대출원금 × (1 − 할인율 A/100)</t>
@@ -743,6 +761,9 @@
   </si>
   <si>
     <t xml:space="preserve">                       · 신규 필드 (최초 대출원금·매각 기준·할인율 A/B·연체이자·1순위 권리자/채권최고액)</t>
+  </si>
+  <si>
+    <t>· v3.3 (2026-04-28) · 수익권 비율 (%) 사용자 설정 + 수익권금액 직접 입력 옵션 (자동값 참고용 분리)</t>
   </si>
   <si>
     <t>10. 문의</t>
@@ -1298,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1554,8 +1575,8 @@
       <c r="A28" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="9">
-        <f>B23*1.4</f>
+      <c r="B28" s="10">
+        <v>140</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>47</v>
@@ -1565,8 +1586,8 @@
       <c r="A29" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>9</v>
+      <c r="B29" s="9">
+        <f>B23*B28/100</f>
       </c>
       <c r="C29" s="3" t="s">
         <v>49</v>
@@ -1576,7 +1597,7 @@
       <c r="A30" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1587,69 +1608,69 @@
       <c r="A31" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>56</v>
       </c>
+      <c r="B33" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="A35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -1664,43 +1685,43 @@
         <v>9</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="A41" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>69</v>
       </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1711,8 +1732,8 @@
       <c r="A45" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="11">
-        <f>IFERROR((B44+B24)/B34*100, "")</f>
+      <c r="B45" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>73</v>
@@ -1722,7 +1743,7 @@
       <c r="A46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -1733,69 +1754,69 @@
       <c r="A47" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>9</v>
+      <c r="B47" s="11">
+        <f>IFERROR((B46+B24)/B36*100, "")</f>
       </c>
       <c r="C47" s="3" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>79</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="A51" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="B51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>84</v>
       </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -1806,8 +1827,8 @@
       <c r="A55" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B55" s="9">
-        <f>B24*(1-B53/100)</f>
+      <c r="B55" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>88</v>
@@ -1817,8 +1838,8 @@
       <c r="A56" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B56" s="9">
-        <f>B27*(1-B54/100)</f>
+      <c r="B56" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>90</v>
@@ -1828,8 +1849,8 @@
       <c r="A57" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>9</v>
+      <c r="B57" s="9">
+        <f>B24*(1-B55/100)</f>
       </c>
       <c r="C57" s="3" t="s">
         <v>92</v>
@@ -1840,7 +1861,7 @@
         <v>93</v>
       </c>
       <c r="B58" s="9">
-        <f>B57*0.1</f>
+        <f>B27*(1-B56/100)</f>
       </c>
       <c r="C58" s="3" t="s">
         <v>94</v>
@@ -1850,7 +1871,7 @@
       <c r="A59" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -1861,27 +1882,27 @@
       <c r="A60" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B60" s="12" t="s">
-        <v>9</v>
+      <c r="B60" s="9">
+        <f>B59*0.1</f>
       </c>
       <c r="C60" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>9</v>
@@ -1892,24 +1913,46 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B63" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1919,9 +1962,9 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A53:C53"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" sqref="B11">
@@ -1936,14 +1979,14 @@
     <dataValidation type="list" allowBlank="1" sqref="B20">
       <formula1>"동일인 (채무자 = 소유자),다름 (물상보증·제3자 담보)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B52">
+    <dataValidation type="list" allowBlank="1" sqref="B54">
       <formula1>"대출원금 기준 (PRINCIPAL),채권잔액 기준 (CLAIM_BALANCE)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B59:B62">
-      <formula1>"O (해당),X (비해당)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B6">
       <formula1>"은행,저축은행,AMC,캐피탈,카드,보험,신협,새마을,신탁,대부업,기타"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B61:B64">
+      <formula1>"O (해당),X (비해당)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B7">
       <formula1>"NPL (부실채권),GENERAL (일반 부동산)"</formula1>
@@ -1971,7 +2014,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1980,7 +2023,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1989,27 +2032,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C4" s="14">
         <v>-60</v>
@@ -2018,15 +2061,15 @@
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C5" s="14">
         <v>-50</v>
@@ -2035,15 +2078,15 @@
         <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C6" s="14">
         <v>-45</v>
@@ -2052,15 +2095,15 @@
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C7" s="14">
         <v>-45</v>
@@ -2069,15 +2112,15 @@
         <v>9</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C8" s="14">
         <v>-40</v>
@@ -2086,15 +2129,15 @@
         <v>9</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C9" s="14">
         <v>-40</v>
@@ -2103,15 +2146,15 @@
         <v>9</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C10" s="14">
         <v>-35</v>
@@ -2120,15 +2163,15 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C11" s="14">
         <v>-30</v>
@@ -2137,15 +2180,15 @@
         <v>9</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C12" s="14">
         <v>-30</v>
@@ -2154,15 +2197,15 @@
         <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C13" s="14">
         <v>-30</v>
@@ -2171,15 +2214,15 @@
         <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C14" s="14">
         <v>-20</v>
@@ -2188,15 +2231,15 @@
         <v>9</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C15" s="14">
         <v>-18</v>
@@ -2205,15 +2248,15 @@
         <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C16" s="14">
         <v>-45</v>
@@ -2222,15 +2265,15 @@
         <v>9</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C17" s="14">
         <v>-35</v>
@@ -2239,15 +2282,15 @@
         <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C18" s="14">
         <v>-30</v>
@@ -2256,15 +2299,15 @@
         <v>9</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C19" s="14">
         <v>-30</v>
@@ -2273,15 +2316,15 @@
         <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C20" s="14">
         <v>-25</v>
@@ -2290,15 +2333,15 @@
         <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C21" s="14">
         <v>-20</v>
@@ -2307,15 +2350,15 @@
         <v>9</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -2324,7 +2367,7 @@
         <f>MAX(20, 100 + SUMPRODUCT((D4:D21="O (해당)")*C4:C21))</f>
       </c>
       <c r="E23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2359,7 +2402,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2368,7 +2411,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2377,47 +2420,47 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>9</v>
@@ -2428,30 +2471,30 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>9</v>
@@ -2462,13 +2505,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>9</v>
@@ -2479,13 +2522,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>9</v>
@@ -2496,30 +2539,30 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>9</v>
@@ -2530,13 +2573,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>9</v>
@@ -2547,13 +2590,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>9</v>
@@ -2564,13 +2607,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>9</v>
@@ -2581,13 +2624,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>9</v>
@@ -2598,30 +2641,30 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>9</v>
@@ -2632,13 +2675,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>9</v>
@@ -2649,13 +2692,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
@@ -2666,30 +2709,30 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>9</v>
@@ -2700,13 +2743,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>9</v>
@@ -2717,13 +2760,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>9</v>
@@ -2734,13 +2777,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>9</v>
@@ -2751,13 +2794,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>9</v>
@@ -2768,13 +2811,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>9</v>
@@ -2813,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2822,7 +2865,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -2834,7 +2877,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -2843,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2851,7 +2894,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2859,7 +2902,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2867,7 +2910,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2878,7 +2921,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B9" s="19"/>
     </row>
@@ -2887,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2895,7 +2938,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2903,7 +2946,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2911,7 +2954,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2919,7 +2962,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2927,7 +2970,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2935,43 +2978,43 @@
         <v>9</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="18"/>
+      <c r="B17" s="18" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="19"/>
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>208</v>
-      </c>
+      <c r="B19" s="18"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>209</v>
-      </c>
+      <c r="A20" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="19"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2979,43 +3022,43 @@
         <v>9</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="18"/>
+      <c r="B23" s="18" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="B24" s="19"/>
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>213</v>
-      </c>
+      <c r="B25" s="18"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>214</v>
-      </c>
+      <c r="A26" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" s="19"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -3023,43 +3066,43 @@
         <v>9</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="18"/>
+      <c r="B29" s="18" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B30" s="19"/>
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>218</v>
-      </c>
+      <c r="B31" s="18"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>219</v>
-      </c>
+      <c r="A32" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="19"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -3067,7 +3110,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3075,51 +3118,51 @@
         <v>9</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="18"/>
+      <c r="B36" s="20" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="19"/>
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>224</v>
-      </c>
+      <c r="B38" s="18"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>225</v>
-      </c>
+      <c r="A39" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="20" t="s">
-        <v>226</v>
+      <c r="B40" s="18" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>227</v>
+      <c r="B41" s="18" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -3127,115 +3170,115 @@
         <v>9</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>229</v>
+      <c r="B43" s="20" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="18" t="s">
-        <v>230</v>
+      <c r="B44" s="20" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="18"/>
+      <c r="B45" s="18" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B46" s="19"/>
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>232</v>
-      </c>
+      <c r="B47" s="18"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>233</v>
-      </c>
+      <c r="A48" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" s="19"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="18"/>
+      <c r="B49" s="18" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="B50" s="19"/>
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="18" t="s">
-        <v>235</v>
-      </c>
+      <c r="B51" s="18"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>236</v>
-      </c>
+      <c r="A52" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52" s="19"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="18"/>
+      <c r="B53" s="18" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B54" s="19"/>
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="18" t="s">
-        <v>238</v>
-      </c>
+      <c r="B55" s="18"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>239</v>
-      </c>
+      <c r="A56" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" s="19"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -3243,35 +3286,59 @@
         <v>9</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="B59" s="20" t="s">
-        <v>242</v>
+      <c r="B59" s="18" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
-      <c r="B60" s="18"/>
+      <c r="B60" s="18" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="B61" s="19"/>
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="18"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="B64" s="19"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3279,14 +3346,14 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A64:B64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/public/templates/NPLatform_매물등록_템플릿.xlsx
+++ b/public/templates/NPLatform_매물등록_템플릿.xlsx
@@ -6,15 +6,13 @@
   <sheets>
     <sheet sheetId="1" name="1_기본정보" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="2_특수조건V2" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="3_필요서류_사진" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="4_가이드_OCR" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="158">
   <si>
     <t>[시트 1] 매물 기본 정보 — NPL 매물등록 템플릿 v3.3 (드롭다운+O/X+수식+수익권 커스텀)</t>
   </si>
@@ -64,7 +62,7 @@
     <t>NPLatform 전속계약 (드롭다운 선택)</t>
   </si>
   <si>
-    <t>전속 ON 시 수수료 0.3% 자동 + 땅집고 기사 지원</t>
+    <t>전속 ON 시 수수료 0.5% 자동 + 땅집고옥션 마케팅 지원</t>
   </si>
   <si>
     <t>2. 담보·주소</t>
@@ -340,7 +338,7 @@
     <t>희망 수수료율 (%)</t>
   </si>
   <si>
-    <t>일반 0.5~0.9 · 전속 시 0.3 자동 적용 (빈칸 허용)</t>
+    <t>일반 0.7~0.9 · 전속 시 0.5 자동 적용 (빈칸 허용)</t>
   </si>
   <si>
     <t>[시트 2] 특수조건 V2 18항목 — O/X 체크리스트 + 점수 자동계산</t>
@@ -488,295 +486,13 @@
   </si>
   <si>
     <t>= MAX(20, 100 + Σ(O 표시 행의 감점))</t>
-  </si>
-  <si>
-    <t>[시트 3] 필요서류 체크리스트</t>
-  </si>
-  <si>
-    <t>구분</t>
-  </si>
-  <si>
-    <t>서류명</t>
-  </si>
-  <si>
-    <t>필수 여부</t>
-  </si>
-  <si>
-    <t>제공 여부</t>
-  </si>
-  <si>
-    <t>파일명 · 첨부 위치</t>
-  </si>
-  <si>
-    <t>필수</t>
-  </si>
-  <si>
-    <t>채권원인서류 사본 (대출계약서·이행약정서)</t>
-  </si>
-  <si>
-    <t>선택</t>
-  </si>
-  <si>
-    <t>예: 대출계약서.pdf</t>
-  </si>
-  <si>
-    <t>채권잔액확인서</t>
-  </si>
-  <si>
-    <t>등기부등본 (부동산 · 최근 1개월 내)</t>
-  </si>
-  <si>
-    <t>필수 자료 — 등기 권리관계 검증 근거</t>
-  </si>
-  <si>
-    <t>건축물대장</t>
-  </si>
-  <si>
-    <t>토지대장</t>
-  </si>
-  <si>
-    <t>공시지가·시가표준액 확인</t>
-  </si>
-  <si>
-    <t>감정평가서 (공인감정평가법인)</t>
-  </si>
-  <si>
-    <t>제공 시 자료 완성도 +10</t>
-  </si>
-  <si>
-    <t>권리분석 보고서</t>
-  </si>
-  <si>
-    <t>임차현황 조사서 (주민등록·확정일자)</t>
-  </si>
-  <si>
-    <t>세금 체납 확인서 (당해세·일반세)</t>
-  </si>
-  <si>
-    <t>4대보험 체납확인서</t>
-  </si>
-  <si>
-    <t>재무제표 (법인 채무자인 경우)</t>
-  </si>
-  <si>
-    <t>경매</t>
-  </si>
-  <si>
-    <t>경매사건기록 (사건번호·관할법원)</t>
-  </si>
-  <si>
-    <t>경매 진행 시</t>
-  </si>
-  <si>
-    <t>감정평가서 (경매법원 제출본)</t>
-  </si>
-  <si>
-    <t>입찰기일 공고</t>
-  </si>
-  <si>
-    <t>공매</t>
-  </si>
-  <si>
-    <t>공매관리번호 / 자산관리공사 공고</t>
-  </si>
-  <si>
-    <t>사진</t>
-  </si>
-  <si>
-    <t>외관 전경 (주 정면)</t>
-  </si>
-  <si>
-    <t>필수 사진 — 최소 1장 · JPG/PNG · 2MB 이하 권장</t>
-  </si>
-  <si>
-    <t>외관 측면 (골목·진입로)</t>
-  </si>
-  <si>
-    <t>내부 거실/주방</t>
-  </si>
-  <si>
-    <t>내부 방·화장실</t>
-  </si>
-  <si>
-    <t>주변 환경·인근 시설</t>
-  </si>
-  <si>
-    <t>하자·흠결 부위 (있을 시)</t>
-  </si>
-  <si>
-    <t>건물대장·등기부 사진 또는 스캔</t>
-  </si>
-  <si>
-    <t>[시트 4] 입력 가이드 · OCR 규격 (v3.3 · 드롭다운 + O/X + 자동계산 + 수익권 커스텀)</t>
-  </si>
-  <si>
-    <t>1. 입력 형식 구분</t>
-  </si>
-  <si>
-    <t>🟦 드롭다운 : 셀을 클릭하면 화살표가 보이고 옵션 목록에서 선택 (예: 시도·기관유형·담보종류·매각기준)</t>
-  </si>
-  <si>
-    <t>🟨 자유 입력 : 금액·면적·날짜·주소·텍스트</t>
-  </si>
-  <si>
-    <t>🟩 O/X 체크 : "O (해당)" / "X (비해당)" 드롭다운 (예: 매각방식·특수조건·서류 제공)</t>
-  </si>
-  <si>
-    <t>⬜ 자동 계산 : 수식 셀 (이탤릭 · 회색 배경) — 직접 입력 금지 · 다른 입력값 변경 시 자동 갱신</t>
-  </si>
-  <si>
-    <t>2. 자동 계산 항목 (시트 1)</t>
-  </si>
-  <si>
-    <t>· 채권잔액 = 대출원금 + 미수이자 + 연체이자</t>
-  </si>
-  <si>
-    <t>· 수익권 비율 (%) = 본인 설정 (110~140 표준 · 기본 140)</t>
-  </si>
-  <si>
-    <t>· 수익권금액 (자동값) = 최초 대출원금 × 수익권 비율%</t>
-  </si>
-  <si>
-    <t>· 수익권금액 (적용값) = 직접 입력 가능 (비우면 자동값 적용 · 매도자 협상가/등기부 채권최고액 우선 시 사용)</t>
-  </si>
-  <si>
-    <t>· 매각가 옵션 A = 대출원금 × (1 − 할인율 A/100)</t>
-  </si>
-  <si>
-    <t>· 매각가 옵션 B = 채권잔액 × (1 − 할인율 B/100)</t>
-  </si>
-  <si>
-    <t>· 계약금 = 매각 희망가 × 10%</t>
-  </si>
-  <si>
-    <t>· LTV (%) = (선순위 채권총액 + 대출원금) ÷ 감정가 × 100</t>
-  </si>
-  <si>
-    <t>· 권리관계 기초점수 (시트 2) = MAX(20, 100 + Σ(O 표시 행의 감점))</t>
-  </si>
-  <si>
-    <t>3. 단일/복수 선택</t>
-  </si>
-  <si>
-    <t>· 시도·기관유형·담보종류·전속계약·채무자유형·매각기준 → 단일 선택 (드롭다운)</t>
-  </si>
-  <si>
-    <t>· 매각방식(엔플랫폼·경매·공매·기타) → 각 행별 O/X 체크 (복수 선택 가능)</t>
-  </si>
-  <si>
-    <t>· 특수조건 18항목 → 각 행별 O/X 체크 (복수 해당 시 모두 O)</t>
-  </si>
-  <si>
-    <t>· 필요서류 · 사진 → 각 행별 O/X 체크 (제공 여부)</t>
-  </si>
-  <si>
-    <t>4. 자유 입력 규칙</t>
-  </si>
-  <si>
-    <t>· 금액: 원 단위 숫자. 쉼표 허용. 단위(억·만) 표기 금지. 예: 1,648,045,960</t>
-  </si>
-  <si>
-    <t>· 날짜: YYYY-MM-DD 고정. 예: 2026-04-28</t>
-  </si>
-  <si>
-    <t>· 면적: ㎡ 단위 숫자. 평 환산값 입력 금지</t>
-  </si>
-  <si>
-    <t>· 비율: % 소수. 예: 4.5</t>
-  </si>
-  <si>
-    <t>5. NPL 매각가 산정 가이드</t>
-  </si>
-  <si>
-    <t>· 케이스 A — 대출원금 기준 매각: 매각 기준 = "대출원금 기준 (PRINCIPAL)" · 할인율 A 입력 (할인율 B 빈칸)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   예) 대출원금 16.48억 × (1 − 5%) = 15.66억 매각</t>
-  </si>
-  <si>
-    <t>· 케이스 B — 채권잔액 기준 매각: 매각 기준 = "채권잔액 기준 (CLAIM_BALANCE)" · 할인율 B 입력 (할인율 A 빈칸)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   예) 채권잔액 17.29억 × 100% (할인 0%) = 17.29억 매각</t>
-  </si>
-  <si>
-    <t>· 매각 희망가 = 옵션 A 또는 B 중 매도자 결정값 (이 값이 거래소·분석에 노출됨)</t>
-  </si>
-  <si>
-    <t>6. OCR 파싱 규격</t>
-  </si>
-  <si>
-    <t>· 시트명 "[시트 N] ..." 형식 고정 → 시트 식별자</t>
-  </si>
-  <si>
-    <t>· 시트 1 : A 열 라벨 · B 열 값. 섹션 머리 (네이비 배경) 기준 그룹화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           드롭다운 셀 값 → 문자열 그대로 파싱 (괄호 안 영문 코드 추출: PRINCIPAL/CLAIM_BALANCE 등)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           수식 셀 → 계산된 값(value) 추출 (formula 무시)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           O/X 체크 셀 → "O" · "해당" → true, 나머지 → false</t>
-  </si>
-  <si>
-    <t>· 시트 2 : 18항목 각 행의 D 열(체크 O/X) 만 읽어 V2 key 매핑</t>
-  </si>
-  <si>
-    <t>· 시트 3 : 각 행의 D 열(제공 O/X) → provided_fields 자동 생성</t>
-  </si>
-  <si>
-    <t>7. 제출 방법</t>
-  </si>
-  <si>
-    <t>· 엑셀 + 사진·서류 폴더를 압축해 NPLatform 담당자에게 전달</t>
-  </si>
-  <si>
-    <t>· 접수 후 1~2 영업일 내 OCR 파싱 결과를 매도자에게 미리보기로 송부</t>
-  </si>
-  <si>
-    <t>8. 수수료 정책 (Phase G6+)</t>
-  </si>
-  <si>
-    <t>· 일반 매물    : 0.5% ~ 0.9% 범위에서 자유 설정</t>
-  </si>
-  <si>
-    <t>· 전속 계약   : 0.3% 자동 적용 + 조선일보 땅집고 기사 지원</t>
-  </si>
-  <si>
-    <t>9. 버전 이력</t>
-  </si>
-  <si>
-    <t>· v1.0 (2026-04-24) · 초기 · 자유입력 기반</t>
-  </si>
-  <si>
-    <t>· v2.0 (2026-04-24) · 체크박스 ☐ 행렬 방식</t>
-  </si>
-  <si>
-    <t>· v3.0 (2026-04-24) · 드롭다운(단일) + O/X 체크(이분) · ExcelJS Data Validation</t>
-  </si>
-  <si>
-    <t>· v3.2 (2026-04-28) · 자동계산 수식 추가 (채권잔액·수익권금액·매각가A/B·LTV·권리관계점수)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                       · 신규 필드 (최초 대출원금·매각 기준·할인율 A/B·연체이자·1순위 권리자/채권최고액)</t>
-  </si>
-  <si>
-    <t>· v3.3 (2026-04-28) · 수익권 비율 (%) 사용자 설정 + 수익권금액 직접 입력 옵션 (자동값 참고용 분리)</t>
-  </si>
-  <si>
-    <t>10. 문의</t>
-  </si>
-  <si>
-    <t>· NPLatform 운영팀 / biz@transfarmer.co.kr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -831,29 +547,6 @@
       <i/>
       <color rgb="FF1B3A5C"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF64748B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <color rgb="FF14161A"/>
-    </font>
-    <font>
-      <color rgb="FF475569"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF14161A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="FF334155"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -926,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -971,15 +664,6 @@
     <xf numFmtId="1" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1992,7 +1676,7 @@
       <formula1>"NPL (부실채권),GENERAL (일반 부동산)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B8">
-      <formula1>"전속 ON (수수료 0.3% + 땅집고 기사 지원),전속 OFF (0.5%~0.9% 자유)"</formula1>
+      <formula1>"전속 ON (수수료 0.5% + 땅집고옥션 마케팅 지원),전속 OFF (0.7%~0.9% 자유)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2386,976 +2070,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A28:E28"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D10:D26">
-      <formula1>"O (제공),X (미제공)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D26">
-      <formula1>"O (제공),X (미제공)"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B65"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="18"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" s="19"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="18"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="19"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="18"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="19"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="18"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" s="19"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="18"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B32" s="19"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="18"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B39" s="19"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="18"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B48" s="19"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="18"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B52" s="19"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="18"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="B56" s="19"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" s="18"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="B64" s="19"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>251</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A64:B64"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>